--- a/input.xlsx
+++ b/input.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ELFANI\scrapper-ccc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B001C60B-AACA-4B83-9FB8-3230465ECB03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C092BC2F-A0D1-4348-8E24-8942A4BFB8BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{528AC7EE-EED8-4251-879B-0C9684AA745D}"/>
+    <workbookView xWindow="330" yWindow="1545" windowWidth="24390" windowHeight="12285" xr2:uid="{528AC7EE-EED8-4251-879B-0C9684AA745D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -56,9 +56,6 @@
     <t>2HGFC2F6XLH600289</t>
   </si>
   <si>
-    <t>04711TBAA50ZZ, 04711TEGA50ZZ</t>
-  </si>
-  <si>
     <t xml:space="preserve">2HGFC2F54HH551668  </t>
   </si>
   <si>
@@ -72,6 +69,9 @@
   </si>
   <si>
     <t>5TFRZ5CN4JX064777</t>
+  </si>
+  <si>
+    <t>04711TBAA50ZZ</t>
   </si>
 </sst>
 </file>
@@ -549,28 +549,28 @@
         <v>4</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>6</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>8</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B6" s="3">
         <v>5381204120</v>

--- a/input.xlsx
+++ b/input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ELFANI\scrapper-ccc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C092BC2F-A0D1-4348-8E24-8942A4BFB8BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1F39390-A590-4E05-99BD-0B2D12620CD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="330" yWindow="1545" windowWidth="24390" windowHeight="12285" xr2:uid="{528AC7EE-EED8-4251-879B-0C9684AA745D}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="34">
   <si>
     <t>VIN</t>
   </si>
@@ -47,31 +47,100 @@
     <t>OEM</t>
   </si>
   <si>
-    <t xml:space="preserve">1HGCV3F44KA012211 </t>
-  </si>
-  <si>
-    <t>04711TVAA00ZZ</t>
-  </si>
-  <si>
-    <t>2HGFC2F6XLH600289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2HGFC2F54HH551668  </t>
-  </si>
-  <si>
-    <t>71121TBAA01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1HGCV1F33LA092436 </t>
-  </si>
-  <si>
-    <t>60260TVAA00ZZ</t>
-  </si>
-  <si>
-    <t>5TFRZ5CN4JX064777</t>
-  </si>
-  <si>
-    <t>04711TBAA50ZZ</t>
+    <t xml:space="preserve">KNDPM3AC0H7049344    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">5J8YD3H3XJL006347 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">KNDCB3LC6K5244255 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2G1FB1E39D9148021 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2C3CCAAG0LH239364  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JF2SKADC3LH603769    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3N1AB8BV7MY283632   </t>
+  </si>
+  <si>
+    <t>5XYRG4LC3NG146409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5NPLL4AG1PH089923 </t>
+  </si>
+  <si>
+    <t>5NMS24AJ8PH493907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JTERU5JR8P6133274    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">KNDPC3A22C7182593  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">jthbf1d28f5079193  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">KMHCT5AE2GU251547  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JTHBW1GG6G2105039   </t>
+  </si>
+  <si>
+    <t>3VWD17AJ0EM438890</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5J6RT6H89NL053758 </t>
+  </si>
+  <si>
+    <t>92101D9111</t>
+  </si>
+  <si>
+    <t>33150TZ5A51</t>
+  </si>
+  <si>
+    <t>92102G5040</t>
+  </si>
+  <si>
+    <t>92101G5040</t>
+  </si>
+  <si>
+    <t>68214383AD</t>
+  </si>
+  <si>
+    <t>84001SJ060</t>
+  </si>
+  <si>
+    <t>260106LB0A</t>
+  </si>
+  <si>
+    <t>92102R5000</t>
+  </si>
+  <si>
+    <t>92101AB000</t>
+  </si>
+  <si>
+    <t>92101-S2500</t>
+  </si>
+  <si>
+    <t>921013W150</t>
+  </si>
+  <si>
+    <t>921021R710</t>
+  </si>
+  <si>
+    <t>8114033A50</t>
+  </si>
+  <si>
+    <t>5C7941006</t>
+  </si>
+  <si>
+    <t>33100TLAA11</t>
   </si>
 </sst>
 </file>
@@ -100,12 +169,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor rgb="FF00B0F0"/>
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -113,26 +182,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -140,10 +194,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -537,245 +596,343 @@
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+      <c r="B3" s="7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B4" s="7" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="7">
+        <v>22959917</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="3">
-        <v>5381204120</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B8" s="4"/>
-    </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B18" s="4"/>
+      <c r="B11" s="7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="7">
+        <v>8107035600</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" s="7">
+        <v>8114553721</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="38" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B38" s="4"/>
+      <c r="B38" s="3"/>
     </row>
     <row r="39" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B39" s="4"/>
+      <c r="B39" s="3"/>
     </row>
     <row r="55" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B55" s="4"/>
+      <c r="B55" s="3"/>
     </row>
     <row r="59" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B59" s="4"/>
+      <c r="B59" s="3"/>
     </row>
     <row r="60" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B60" s="4"/>
+      <c r="B60" s="3"/>
     </row>
     <row r="107" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B107" s="4"/>
+      <c r="B107" s="3"/>
     </row>
     <row r="108" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B108" s="4"/>
+      <c r="B108" s="3"/>
     </row>
     <row r="114" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B114" s="4"/>
+      <c r="B114" s="3"/>
     </row>
     <row r="115" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B115" s="4"/>
+      <c r="B115" s="3"/>
     </row>
     <row r="140" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B140" s="4"/>
+      <c r="B140" s="3"/>
     </row>
     <row r="141" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B141" s="4"/>
+      <c r="B141" s="3"/>
     </row>
     <row r="142" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B142" s="4"/>
+      <c r="B142" s="3"/>
     </row>
     <row r="143" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B143" s="4"/>
+      <c r="B143" s="3"/>
     </row>
     <row r="152" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B152" s="4"/>
+      <c r="B152" s="3"/>
     </row>
     <row r="187" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B187" s="4"/>
+      <c r="B187" s="3"/>
     </row>
     <row r="208" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B208" s="4"/>
+      <c r="B208" s="3"/>
     </row>
     <row r="213" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B213" s="4"/>
+      <c r="B213" s="3"/>
     </row>
     <row r="214" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B214" s="4"/>
+      <c r="B214" s="3"/>
     </row>
     <row r="226" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B226" s="4"/>
+      <c r="B226" s="3"/>
     </row>
     <row r="237" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B237" s="4"/>
+      <c r="B237" s="3"/>
     </row>
     <row r="259" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B259" s="4"/>
+      <c r="B259" s="3"/>
     </row>
     <row r="277" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B277" s="4"/>
+      <c r="B277" s="3"/>
     </row>
     <row r="294" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B294" s="4"/>
+      <c r="B294" s="3"/>
     </row>
     <row r="298" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B298" s="4"/>
+      <c r="B298" s="3"/>
     </row>
     <row r="323" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B323" s="4"/>
+      <c r="B323" s="3"/>
     </row>
     <row r="398" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B398" s="4"/>
+      <c r="B398" s="3"/>
     </row>
     <row r="406" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B406" s="4"/>
+      <c r="B406" s="3"/>
     </row>
     <row r="409" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B409" s="4"/>
+      <c r="B409" s="3"/>
     </row>
     <row r="414" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B414" s="4"/>
+      <c r="B414" s="3"/>
     </row>
     <row r="423" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B423" s="4"/>
+      <c r="B423" s="3"/>
     </row>
     <row r="456" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B456" s="4"/>
+      <c r="B456" s="3"/>
     </row>
     <row r="457" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B457" s="4"/>
+      <c r="B457" s="3"/>
     </row>
     <row r="458" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B458" s="4"/>
+      <c r="B458" s="3"/>
     </row>
     <row r="459" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B459" s="4"/>
+      <c r="B459" s="3"/>
     </row>
     <row r="462" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B462" s="4"/>
+      <c r="B462" s="3"/>
     </row>
     <row r="474" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B474" s="4"/>
+      <c r="B474" s="3"/>
     </row>
     <row r="500" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B500" s="4"/>
+      <c r="B500" s="3"/>
     </row>
     <row r="503" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B503" s="4"/>
+      <c r="B503" s="3"/>
     </row>
     <row r="533" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B533" s="4"/>
+      <c r="B533" s="3"/>
     </row>
     <row r="552" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B552" s="4"/>
+      <c r="B552" s="3"/>
     </row>
     <row r="553" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B553" s="4"/>
+      <c r="B553" s="3"/>
     </row>
     <row r="560" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B560" s="4"/>
+      <c r="B560" s="3"/>
     </row>
     <row r="588" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B588" s="4"/>
+      <c r="B588" s="3"/>
     </row>
     <row r="600" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B600" s="4"/>
+      <c r="B600" s="3"/>
     </row>
     <row r="697" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B697" s="4"/>
+      <c r="B697" s="3"/>
     </row>
     <row r="698" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B698" s="4"/>
+      <c r="B698" s="3"/>
     </row>
     <row r="699" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B699" s="4"/>
+      <c r="B699" s="3"/>
     </row>
     <row r="700" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B700" s="4"/>
+      <c r="B700" s="3"/>
     </row>
     <row r="701" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B701" s="4"/>
+      <c r="B701" s="3"/>
     </row>
     <row r="702" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B702" s="4"/>
+      <c r="B702" s="3"/>
     </row>
     <row r="703" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B703" s="4"/>
+      <c r="B703" s="3"/>
     </row>
     <row r="704" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B704" s="4"/>
+      <c r="B704" s="3"/>
     </row>
     <row r="705" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B705" s="4"/>
+      <c r="B705" s="3"/>
     </row>
     <row r="706" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B706" s="4"/>
+      <c r="B706" s="3"/>
     </row>
     <row r="707" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B707" s="4"/>
+      <c r="B707" s="3"/>
     </row>
     <row r="708" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B708" s="4"/>
+      <c r="B708" s="3"/>
     </row>
     <row r="709" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B709" s="4"/>
+      <c r="B709" s="3"/>
     </row>
     <row r="710" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B710" s="4"/>
+      <c r="B710" s="3"/>
     </row>
     <row r="711" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B711" s="4"/>
+      <c r="B711" s="3"/>
     </row>
     <row r="730" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B730" s="4"/>
+      <c r="B730" s="3"/>
     </row>
     <row r="731" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B731" s="4"/>
+      <c r="B731" s="3"/>
     </row>
     <row r="732" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B732" s="4"/>
+      <c r="B732" s="3"/>
     </row>
     <row r="735" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B735" s="4"/>
+      <c r="B735" s="3"/>
     </row>
     <row r="737" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B737" s="4"/>
+      <c r="B737" s="3"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A7:A207">
+  <conditionalFormatting sqref="A20:A207">
     <cfRule type="duplicateValues" dxfId="3" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A232:A240">

--- a/input.xlsx
+++ b/input.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ELFANI\scrapper-ccc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1F39390-A590-4E05-99BD-0B2D12620CD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF973F47-7EDB-4C51-B9E4-5038398566EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="330" yWindow="1545" windowWidth="24390" windowHeight="12285" xr2:uid="{528AC7EE-EED8-4251-879B-0C9684AA745D}"/>
+    <workbookView xWindow="675" yWindow="2520" windowWidth="24390" windowHeight="12285" xr2:uid="{528AC7EE-EED8-4251-879B-0C9684AA745D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>VIN</t>
   </si>
@@ -47,100 +47,28 @@
     <t>OEM</t>
   </si>
   <si>
-    <t xml:space="preserve">KNDPM3AC0H7049344    </t>
-  </si>
-  <si>
-    <t xml:space="preserve">5J8YD3H3XJL006347 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">KNDCB3LC6K5244255 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2G1FB1E39D9148021 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2C3CCAAG0LH239364  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">JF2SKADC3LH603769    </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3N1AB8BV7MY283632   </t>
-  </si>
-  <si>
     <t>5XYRG4LC3NG146409</t>
   </si>
   <si>
-    <t xml:space="preserve">5NPLL4AG1PH089923 </t>
-  </si>
-  <si>
-    <t>5NMS24AJ8PH493907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JTERU5JR8P6133274    </t>
-  </si>
-  <si>
-    <t xml:space="preserve">KNDPC3A22C7182593  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">jthbf1d28f5079193  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">KMHCT5AE2GU251547  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">JTHBW1GG6G2105039   </t>
-  </si>
-  <si>
-    <t>3VWD17AJ0EM438890</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5J6RT6H89NL053758 </t>
-  </si>
-  <si>
-    <t>92101D9111</t>
-  </si>
-  <si>
-    <t>33150TZ5A51</t>
-  </si>
-  <si>
-    <t>92102G5040</t>
-  </si>
-  <si>
-    <t>92101G5040</t>
-  </si>
-  <si>
     <t>68214383AD</t>
   </si>
   <si>
-    <t>84001SJ060</t>
-  </si>
-  <si>
-    <t>260106LB0A</t>
-  </si>
-  <si>
     <t>92102R5000</t>
   </si>
   <si>
-    <t>92101AB000</t>
-  </si>
-  <si>
-    <t>92101-S2500</t>
-  </si>
-  <si>
     <t>921013W150</t>
   </si>
   <si>
-    <t>921021R710</t>
-  </si>
-  <si>
-    <t>8114033A50</t>
-  </si>
-  <si>
-    <t>5C7941006</t>
-  </si>
-  <si>
-    <t>33100TLAA11</t>
+    <t>2C3CCAAG0LH239364</t>
+  </si>
+  <si>
+    <t>JTERU5JR8P6133274</t>
+  </si>
+  <si>
+    <t>8107035600</t>
+  </si>
+  <si>
+    <t>KNDPC3A22C7182593</t>
   </si>
 </sst>
 </file>
@@ -160,18 +88,12 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF00B0F0"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -186,7 +108,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -197,11 +119,7 @@
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -596,148 +514,92 @@
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>20</v>
+      <c r="B3" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>21</v>
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>22</v>
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" s="7">
-        <v>22959917</v>
-      </c>
+      <c r="A6" s="4"/>
+      <c r="B6" s="5"/>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>23</v>
-      </c>
+      <c r="A7" s="4"/>
+      <c r="B7" s="5"/>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>24</v>
-      </c>
+      <c r="A8" s="4"/>
+      <c r="B8" s="5"/>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>25</v>
-      </c>
+      <c r="A9" s="4"/>
+      <c r="B9" s="5"/>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>26</v>
-      </c>
+      <c r="A10" s="4"/>
+      <c r="B10" s="5"/>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>27</v>
-      </c>
+      <c r="A11" s="4"/>
+      <c r="B11" s="5"/>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>28</v>
-      </c>
+      <c r="A12" s="4"/>
+      <c r="B12" s="5"/>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B13" s="7">
-        <v>8107035600</v>
-      </c>
+      <c r="A13" s="4"/>
+      <c r="B13" s="5"/>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>29</v>
-      </c>
+      <c r="A14" s="4"/>
+      <c r="B14" s="5"/>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B15" s="7">
-        <v>8114553721</v>
-      </c>
+      <c r="A15" s="4"/>
+      <c r="B15" s="5"/>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>30</v>
-      </c>
+      <c r="A16" s="4"/>
+      <c r="B16" s="5"/>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>31</v>
-      </c>
+      <c r="A17" s="4"/>
+      <c r="B17" s="5"/>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B18" s="7" t="s">
-        <v>32</v>
-      </c>
+      <c r="A18" s="4"/>
+      <c r="B18" s="5"/>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B19" s="7" t="s">
-        <v>33</v>
-      </c>
+      <c r="A19" s="4"/>
+      <c r="B19" s="5"/>
     </row>
     <row r="38" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B38" s="3"/>
